--- a/sources/anna_step8.xlsx
+++ b/sources/anna_step8.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB136"/>
+  <dimension ref="A1:AB134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col hidden="1" min="4" max="4"/>
     <col width="68" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -434,9 +434,9 @@
     <col width="19" customWidth="1" min="12" max="12"/>
     <col hidden="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
     <col hidden="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="17" max="17"/>
     <col hidden="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
@@ -3526,12 +3526,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>df+1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>df+1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3546,22 +3546,22 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>+1 +1</t>
+          <t>+1 -5</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>+1 +1</t>
+          <t>+1 -5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3586,258 +3586,248 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>4,10</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>4,10</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>mh</t>
+          <t>hh</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>mh</t>
+          <t>hh</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>d0c5a7da-b497-4286-a857-fd8930564a52</t>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>38c084ac-b201-4176-b5c8-6332f4f011fb</t>
+          <t>74320b9b-6947-4250-be78-d728f6f0ae88</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>– 3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Double Punch</t>
+          <t>– Low Kick</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Double Punch</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+          <t>Double Punch – Low Kick</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>+1 -5</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>+1 -5</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>+7 +7</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>+7 +7</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>+7 +7</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>+7 +7</t>
-        </is>
-      </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>4,10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>4,10</t>
+          <t>4,10,10</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>hh</t>
+          <t>l</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>hh</t>
+          <t>hhl</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>RC</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Does not work starting with d/f+1,2</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
+          <t>fefdb095-541f-4d3e-939a-f3c64b7764d5</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>c924ef1d-a211-4681-b97f-c72dcfadc034</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
           <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>74320b9b-6947-4250-be78-d728f6f0ae88</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BT 1,2</t>
+          <t>– 4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BT 1,2</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>BT 2,2</t>
+          <t>1,2,4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Double Punch</t>
+          <t>– Bermuda Triangle</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Double Punch</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
+          <t>Double Punch – Bermuda Triangle</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-8 -5</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-8 -5</t>
+          <t>+1 -5 -19</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>+3 +7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+3 +7</t>
+          <t>+7 +7 KD</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>+3 +7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>+3 +7</t>
+          <t>+7 +7 KD</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>15,10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>15,10</t>
+          <t>4,10,15</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>hh</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>hh</t>
+          <t>hhh</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
+          <t>02cdaf34-b75f-4d9e-8eb0-6c4fa1d43d20</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>88b77f98-207e-4a96-bf95-31b06c11f4ac</t>
+          <t>7bdd8152-f754-413b-93c7-6a475498cf57</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>– 3</t>
+          <t>– 1,4,2 [~U_~D]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BT 1,2,3</t>
+          <t>1,2,1,4,2 [~U_~D]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>– Low Kick</t>
+          <t>– Snake [SS]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Double Punch – Low Kick</t>
+          <t>Double Punch – Snake [SS]</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3845,91 +3835,101 @@
           <t>8</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>+1 0 +2</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-8 -5</t>
+          <t>+1 -5 +1 0 +2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>+12 -2 0</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+3 +7</t>
+          <t>+7 +7 +12 -2 0</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>+12 -2 0</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>+3 +7</t>
+          <t>+7 +7 +12 -2 0</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6,15,12</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>33</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>15,10,10</t>
+          <t>4,10,6,15,12</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>hhh</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>hhl</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>hhhhh</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Does not work starting with d/f+1,2</t>
+          <t>Side Step can be linked into Chaos Tail or Bloody Choas.</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>fefdb095-541f-4d3e-939a-f3c64b7764d5</t>
+          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>c924ef1d-a211-4681-b97f-c72dcfadc034</t>
+          <t>41065dfb-ba4e-41c9-a420-6d59ce98bf8e</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>– 4</t>
+          <t>–– 3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BT 1,2,4</t>
+          <t>1,2,1,4,2 [~U_~D],3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>– Bermuda Triangle</t>
+          <t>–– High Kick</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Double Punch – Bermuda Triangle</t>
+          <t>Double Punch – Snake [SS] – High Kick</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3939,47 +3939,47 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-8 -5 -19</t>
+          <t>+1 -5 +1 0 +2 0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+3 +7 KD</t>
+          <t>+7 +7 +12 -2 0 +9</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>+3 +7 KD</t>
+          <t>+7 +7 +12 -2 0 +9</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>15,10,15</t>
+          <t>4,10,6,15,12,17</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -3989,44 +3989,49 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>hhh</t>
+          <t>hhhhhh</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>GB</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>02cdaf34-b75f-4d9e-8eb0-6c4fa1d43d20</t>
+          <t>d0568b44-b953-4c64-af12-551ed65bde27</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>7bdd8152-f754-413b-93c7-6a475498cf57</t>
+          <t>e48f0a78-2da9-48e4-8d2d-3e422a9029c9</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
+          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>– 1,4,2 [~U_~D]</t>
+          <t>–– uf+3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BT 1,2,1,4,2 [~U_~D]</t>
+          <t>1,2,1,4,2 [~U_~D],uf+3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>– Snake [SS]</t>
+          <t>–– Bone Cutter</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS]</t>
+          <t>Double Punch – Snake [SS] – Bone Cutter</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4034,39 +4039,24 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>+1 0 +2</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-8 -5 +1 0 +2</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>+12 -2 0</t>
+          <t>+1 -5 +1 0 +2</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+3 +7 +12 -2 0</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>+12 -2 0</t>
+          <t>+7 +7 +12 -2 0</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>+3 +7 +12 -2 0</t>
+          <t>+7 +7 +12 -2 0</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>6,15,12</t>
+          <t>13,10,10</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4076,59 +4066,54 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>15,10,6,15,12</t>
+          <t>4,10,6,15,12,13,10,10</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>hhh</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>hhhhh</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Side Step can be linked into Chaos Tail or Bloody Choas.</t>
+          <t>hhhhhh</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
+          <t>be54fc7b-95ac-42d4-b8b3-fcb452c8baa5</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>07611425-29b3-41ef-8a3f-0717f290a07d</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
           <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>41065dfb-ba4e-41c9-a420-6d59ce98bf8e</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>–– 3</t>
+          <t>–– 4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BT 1,2,1,4,2 [~U_~D],3</t>
+          <t>1,2,1,4,2 [~U_~D],4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>–– High Kick</t>
+          <t>–– Spin Trip</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS] – High Kick</t>
+          <t>Double Punch – Snake [SS] – Spin Trip</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4138,72 +4123,72 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-8 -5 +1 0 +2 0</t>
+          <t>+1 -5 +1 0 +2 -23</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+3 +7 +12 -2 0 +9</t>
+          <t>+7 +7 +12 -2 0 KD</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>+3 +7 +12 -2 0 +9</t>
+          <t>+7 +7 +12 -2 0 KD</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>15,10,6,15,12,17</t>
+          <t>4,10,6,15,12,21</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>L</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>hhhhhh</t>
+          <t>hhhhhL</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>d0568b44-b953-4c64-af12-551ed65bde27</t>
+          <t>caa2d86d-5b50-4cdf-9692-4d547308f93b</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>e48f0a78-2da9-48e4-8d2d-3e422a9029c9</t>
+          <t>166cad2e-2c08-4739-b7e4-1e2d60f6a73b</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -4215,22 +4200,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>–– uf+3</t>
+          <t>– 1,b+4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BT 1,2,1,4,2 [~U_~D],uf+3</t>
+          <t>1,2,1,b+4</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>–– Bone Cutter</t>
+          <t>– Jab Rush - Low Kick</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS] – Bone Cutter</t>
+          <t>Double Punch – Jab Rush - Low Kick</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4238,81 +4223,106 @@
           <t>8</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>+1 -10</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-8 -5 +1 0 +2</t>
+          <t>+1 -5 +1 -10</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>+12 +1</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+3 +7 +12 -2 0</t>
+          <t>+7 +7 +12 +1</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>+12 +1</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>+3 +7 +12 -2 0</t>
+          <t>+7 +7 +12 +1</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>13,10,10</t>
+          <t>6,8</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>15,10,6,15,12,13,10,10</t>
+          <t>4,10,6,8</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>hl</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>hhhhhh</t>
+          <t>hhhl</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>be54fc7b-95ac-42d4-b8b3-fcb452c8baa5</t>
+          <t>1b40f311-91f7-4a46-be3b-81978d302f90</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>07611425-29b3-41ef-8a3f-0717f290a07d</t>
+          <t>b301db8a-cbb4-4227-a630-d5ca1ba4fe0e</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>–– 4</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BT 1,2,1,4,2 [~U_~D],4</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>–– Spin Trip</t>
+          <t>PDK Combo</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS] – Spin Trip</t>
+          <t>PDK Combo</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4322,201 +4332,196 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>+1 -10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-8 -5 +1 0 +2 -23</t>
+          <t>+1 -10</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+7 +1</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+3 +7 +12 -2 0 KD</t>
+          <t>+7 +1</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+7 +1</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>+3 +7 +12 -2 0 KD</t>
+          <t>+7 +1</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4,8</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>15,10,6,15,12,21</t>
+          <t>4,8</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>hl</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>hhhhhL</t>
+          <t>hl</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>caa2d86d-5b50-4cdf-9692-4d547308f93b</t>
+          <t>3db16d2c-f04e-40cb-a74c-ecbfde854d6d</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>166cad2e-2c08-4739-b7e4-1e2d60f6a73b</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
+          <t>eb2690e4-5fed-4120-8ae5-c870948f502d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>– 1,b+4</t>
+          <t>df+1,2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BT 1,2,1,b+4</t>
+          <t>df+1,2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>– Jab Rush - Low Kick</t>
+          <t>Double Punch</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Double Punch – Jab Rush - Low Kick</t>
+          <t>Double Punch</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>+1 -10</t>
+          <t>+1 +1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-8 -5 +1 -10</t>
+          <t>+1 +1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>+12 +1</t>
+          <t>+7 +7</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+3 +7 +12 +1</t>
+          <t>+7 +7</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>+12 +1</t>
+          <t>+7 +7</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>+3 +7 +12 +1</t>
+          <t>+7 +7</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>6,8</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>15,10,6,8</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>hl</t>
+          <t>mh</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>hhhl</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>mh</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>1b40f311-91f7-4a46-be3b-81978d302f90</t>
+          <t>d0c5a7da-b497-4286-a857-fd8930564a52</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>b301db8a-cbb4-4227-a630-d5ca1ba4fe0e</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
+          <t>38c084ac-b201-4176-b5c8-6332f4f011fb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>BT 1,2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>BT 1,2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BT 2,2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PDK Combo</t>
+          <t>Double Punch</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PDK Combo</t>
+          <t>Double Punch</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4531,72 +4536,67 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>+1 -10</t>
+          <t>-8 -5</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>+1 -10</t>
+          <t>-8 -5</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>+7 +1</t>
+          <t>+3 +7</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+7 +1</t>
+          <t>+3 +7</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>+7 +1</t>
+          <t>+3 +7</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>+7 +1</t>
+          <t>+3 +7</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>4,8</t>
+          <t>15,10</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>4,8</t>
+          <t>15,10</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>hl</t>
+          <t>hh</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>hl</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>hh</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>3db16d2c-f04e-40cb-a74c-ecbfde854d6d</t>
+          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>eb2690e4-5fed-4120-8ae5-c870948f502d</t>
+          <t>88b77f98-207e-4a96-bf95-31b06c11f4ac</t>
         </is>
       </c>
     </row>
@@ -10921,11 +10921,6 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="X123" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z123" t="inlineStr">
         <is>
           <t>92a0e966-a546-45f7-81d9-9e04d25a558e</t>
@@ -10983,11 +10978,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X124" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z124" t="inlineStr">
         <is>
           <t>487cce17-0598-43ae-841e-c8d65b03adc2</t>
@@ -11045,11 +11035,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z125" t="inlineStr">
         <is>
           <t>01df9a40-ec1c-4c04-abdf-abf4bf803a6a</t>
@@ -11107,11 +11092,6 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z126" t="inlineStr">
         <is>
           <t>cfdb48e8-266a-4483-8dbc-a23b48dbea40</t>
@@ -11169,11 +11149,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z127" t="inlineStr">
         <is>
           <t>ace888c8-b086-4f5e-80f5-f2f0c5dffa97</t>
@@ -11231,11 +11206,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z128" t="inlineStr">
         <is>
           <t>f933e84c-5e2d-4683-b1d5-a29155eeef0b</t>
@@ -11293,11 +11263,6 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="X129" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z129" t="inlineStr">
         <is>
           <t>93714c88-336b-411f-b863-f65c2a39733a</t>
@@ -11353,11 +11318,6 @@
       <c r="U130" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="X130" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
@@ -11568,105 +11528,6 @@
         </is>
       </c>
       <c r="AB134" t="inlineStr">
-        <is>
-          <t>ML only</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>df+1,2,1,2,3,3,2,1,2,4</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>df+1,2,1,2,3,3,2,1,2,4</t>
-        </is>
-      </c>
-      <c r="O135" t="inlineStr">
-        <is>
-          <t>10,15,6,6,7,9,6,6,6,30</t>
-        </is>
-      </c>
-      <c r="P135" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t>10,15,6,6,7,9,6,6,6,30</t>
-        </is>
-      </c>
-      <c r="R135" t="inlineStr">
-        <is>
-          <t>mhhhhlhhhh</t>
-        </is>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>mhhhhlhhhh</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>3868d410-2e89-48d9-953a-b6d47bab49c4</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>ML only</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>BT 1,2,1,2,3,3,2,1,2,4</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>BT 1,2,1,2,3,3,2,1,2,4</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>2,2,1,2,3,3,2,1,2,4</t>
-        </is>
-      </c>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>15,10,6,6,7,9,6,6,6,30</t>
-        </is>
-      </c>
-      <c r="P136" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>15,10,6,6,7,9,6,6,6,30</t>
-        </is>
-      </c>
-      <c r="R136" t="inlineStr">
-        <is>
-          <t>hhhhhlhhhh</t>
-        </is>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>hhhhhlhhhh</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>2f43bade-2f95-4531-9ea3-4cdbb2bdd0bd</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/anna_step8.xlsx
+++ b/sources/anna_step8.xlsx
@@ -425,7 +425,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col hidden="1" min="4" max="4"/>
     <col width="68" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col hidden="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col hidden="1" min="9" max="9"/>
@@ -3812,22 +3812,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>– 1,4,2 [~U_~D]</t>
+          <t>– 1,4,2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1,2,1,4,2 [~U_~D]</t>
+          <t>1,2,1,4,2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>– Snake [SS]</t>
+          <t>– Snake</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS]</t>
+          <t>Double Punch – Snake</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3919,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1,2,1,4,2 [~U_~D],3</t>
+          <t>1,2,1,4,2,3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3929,7 +3934,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS] – High Kick</t>
+          <t>Double Punch – Snake – High Kick</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4021,7 +4026,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1,2,1,4,2 [~U_~D],uf+3</t>
+          <t>1,2,1,4,2,uf+3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4031,7 +4036,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS] – Bone Cutter</t>
+          <t>Double Punch – Snake – Bone Cutter</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4103,7 +4108,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1,2,1,4,2 [~U_~D],4</t>
+          <t>1,2,1,4,2,4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4113,7 +4118,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS] – Spin Trip</t>
+          <t>Double Punch – Snake – Spin Trip</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7660,22 +7665,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>– 4&lt;2 [~U_~D]</t>
+          <t>– 4&lt;2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>df+3,1,4&lt;2 [~U_~D]</t>
+          <t>df+3,1,4&lt;2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>– Snake [SS]</t>
+          <t>– Snake</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Assault – Snake [SS]</t>
+          <t>Assault – Snake</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -7767,7 +7777,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>df+3,1,4&lt;2 [~U_~D],3</t>
+          <t>df+3,1,4&lt;2,3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7777,7 +7787,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Assault – Snake [SS] – High Kick</t>
+          <t>Assault – Snake – High Kick</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7864,7 +7874,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>df+3,1,4&lt;2 [~U_~D],uf+3</t>
+          <t>df+3,1,4&lt;2,uf+3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7874,7 +7884,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Assault – Snake [SS] – Bone Cutter</t>
+          <t>Assault – Snake – Bone Cutter</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7946,7 +7956,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>df+3,1,4&lt;2 [~U_~D],4</t>
+          <t>df+3,1,4&lt;2,4</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7956,7 +7966,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Assault – Snake [SS] – Spin Trip</t>
+          <t>Assault – Snake – Spin Trip</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8140,22 +8150,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D]</t>
+          <t>df+3,2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D]</t>
+          <t>df+3,2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Creeping Snake [SS]</t>
+          <t>Creeping Snake</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Creeping Snake [SS]</t>
+          <t>Creeping Snake</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -8242,7 +8257,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],1,4</t>
+          <t>df+3,2,1,4</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8252,7 +8267,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Creeping Snake [SS] – Biting Snake</t>
+          <t>Creeping Snake – Biting Snake</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8344,7 +8359,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],3</t>
+          <t>df+3,2,3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8354,7 +8369,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Creeping Snake [SS] – High Kick</t>
+          <t>Creeping Snake – High Kick</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8446,7 +8461,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],d+3</t>
+          <t>df+3,2,d+3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8456,7 +8471,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Creeping Snake [SS] – Low Kick</t>
+          <t>Creeping Snake – Low Kick</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8548,7 +8563,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],4</t>
+          <t>df+3,2,4</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8558,7 +8573,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Creeping Snake [SS] – Roundhouse</t>
+          <t>Creeping Snake – Roundhouse</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8759,22 +8774,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>–– 4&lt;2 [~U_~D]</t>
+          <t>–– 4&lt;2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>df+3,3,3,1,4&lt;2 [~U_~D]</t>
+          <t>df+3,3,3,1,4&lt;2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>–– Snake [SS]</t>
+          <t>–– Snake</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Spike Combo – Assault – Snake [SS]</t>
+          <t>Spike Combo – Assault – Snake</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -8831,7 +8851,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>df+3,3,3,1,4&lt;2 [~U_~D],3</t>
+          <t>df+3,3,3,1,4&lt;2,3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8841,7 +8861,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Spike Combo – Assault – Snake [SS] – High Kick</t>
+          <t>Spike Combo – Assault – Snake – High Kick</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -8893,7 +8913,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>df+3,3,3,1,4&lt;2 [~U_~D],uf+3</t>
+          <t>df+3,3,3,1,4&lt;2,uf+3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8903,7 +8923,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Spike Combo – Assault – Snake [SS] – Bone Cutter</t>
+          <t>Spike Combo – Assault – Snake – Bone Cutter</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -8955,7 +8975,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>df+3,3,3,1,4&lt;2 [~U_~D],4</t>
+          <t>df+3,3,3,1,4&lt;2,4</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8965,7 +8985,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Spike Combo – Assault – Snake [SS] – Spin Trip</t>
+          <t>Spike Combo – Assault – Snake – Spin Trip</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -9243,22 +9263,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>uf+4,3,4 [~U_~D]</t>
+          <t>uf+4,3,4</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>uf+4,3,4 [~U_~D]</t>
+          <t>uf+4,3,4</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Can Opener [SS]</t>
+          <t>Can Opener</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Can Opener [SS]</t>
+          <t>Can Opener</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -9345,22 +9370,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>d+4&lt;1 [~U_~D]</t>
+          <t>d+4&lt;1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>d+4&lt;1 [~U_~D]</t>
+          <t>d+4&lt;1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [SS]</t>
+          <t>Shin Kick - Spin Punch</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [SS]</t>
+          <t>Shin Kick - Spin Punch</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -9447,22 +9477,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FC+4,1 [~U_~D]</t>
+          <t>FC+4,1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FC+4,1 [~U_~D]</t>
+          <t>FC+4,1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [SS]</t>
+          <t>Shin Kick - Spin Punch</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [SS]</t>
+          <t>Shin Kick - Spin Punch</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">

--- a/sources/anna_step8.xlsx
+++ b/sources/anna_step8.xlsx
@@ -1000,6 +1000,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>d0af4541-7b9a-41bf-9ff0-5f2b5d4a1a13</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>d0af4541-7b9a-41bf-9ff0-5f2b5d4a1a13</t>
@@ -1062,6 +1067,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1bd5e4f8-ba3c-42b7-8668-d0aacd0a7412</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>1bd5e4f8-ba3c-42b7-8668-d0aacd0a7412</t>
@@ -1122,6 +1132,11 @@
       <c r="U10" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>31ad5619-ed1a-41f7-95e0-e44eadc9aed1</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -10904,6 +10919,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>7e1ce62b-b055-489f-b2df-17938cd65470</t>
+        </is>
+      </c>
       <c r="Z122" t="inlineStr">
         <is>
           <t>7e1ce62b-b055-489f-b2df-17938cd65470</t>
@@ -10956,6 +10976,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>92a0e966-a546-45f7-81d9-9e04d25a558e</t>
+        </is>
+      </c>
       <c r="Z123" t="inlineStr">
         <is>
           <t>92a0e966-a546-45f7-81d9-9e04d25a558e</t>
@@ -11013,6 +11038,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>487cce17-0598-43ae-841e-c8d65b03adc2</t>
+        </is>
+      </c>
       <c r="Z124" t="inlineStr">
         <is>
           <t>487cce17-0598-43ae-841e-c8d65b03adc2</t>
@@ -11070,6 +11100,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>01df9a40-ec1c-4c04-abdf-abf4bf803a6a</t>
+        </is>
+      </c>
       <c r="Z125" t="inlineStr">
         <is>
           <t>01df9a40-ec1c-4c04-abdf-abf4bf803a6a</t>
@@ -11127,6 +11162,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>cfdb48e8-266a-4483-8dbc-a23b48dbea40</t>
+        </is>
+      </c>
       <c r="Z126" t="inlineStr">
         <is>
           <t>cfdb48e8-266a-4483-8dbc-a23b48dbea40</t>
@@ -11184,6 +11224,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>ace888c8-b086-4f5e-80f5-f2f0c5dffa97</t>
+        </is>
+      </c>
       <c r="Z127" t="inlineStr">
         <is>
           <t>ace888c8-b086-4f5e-80f5-f2f0c5dffa97</t>
@@ -11241,6 +11286,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>f933e84c-5e2d-4683-b1d5-a29155eeef0b</t>
+        </is>
+      </c>
       <c r="Z128" t="inlineStr">
         <is>
           <t>f933e84c-5e2d-4683-b1d5-a29155eeef0b</t>
@@ -11298,6 +11348,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>93714c88-336b-411f-b863-f65c2a39733a</t>
+        </is>
+      </c>
       <c r="Z129" t="inlineStr">
         <is>
           <t>93714c88-336b-411f-b863-f65c2a39733a</t>
@@ -11353,6 +11408,11 @@
       <c r="U130" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>0e938de5-6095-4002-9ade-581f69b50247</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
@@ -11555,6 +11615,11 @@
       <c r="S134" t="inlineStr">
         <is>
           <t>hhhhhlhhhh</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>d61c2d77-39a1-494e-8996-5a62586356a9</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
